--- a/output/pdf_financials_xlsx/BLDS.xlsx
+++ b/output/pdf_financials_xlsx/BLDS.xlsx
@@ -5918,49 +5918,49 @@
         <v>0.015</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.58831</v>
+        <v>1.559413</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.941212</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.856765</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.503416</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.374793</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.994333</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.242901</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.270936</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.381501</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.957823</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.015395</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.966871</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.507421</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.629166</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.290871</v>
       </c>
     </row>
     <row r="93">
@@ -9802,7 +9802,11 @@
           <t>Share-based payments reserve 11</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11093,7 +11097,11 @@
           <t>Share-based payments reserve 13</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -12288,7 +12296,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13557,7 +13569,11 @@
           <t>Share-based payments reserve 12</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -16262,7 +16278,11 @@
           <t>Share-based payments reserve 15</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -17175,7 +17195,11 @@
           <t>Share-based payments reserve 14</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -19009,7 +19033,11 @@
           <t>Share-based payments reserve 13 1,941,212</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BLDS.xlsx
+++ b/output/pdf_financials_xlsx/BLDS.xlsx
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00022</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.040564</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.046736</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.014968</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.011888</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000348</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1083,16 +1083,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.000164</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>4.4e-05</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000829</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -2018,22 +2018,22 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.048835</v>
+        <v>-0.049055</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.705899</v>
+        <v>-2.746463</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.553808</v>
+        <v>-3.600544</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-16.190661</v>
+        <v>-16.205629</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.675412</v>
+        <v>-5.6873</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.779215</v>
+        <v>-2.779563</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.734545</v>
@@ -2051,16 +2051,16 @@
         <v>-1.435476</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.117714</v>
+        <v>-1.117878</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.821882</v>
+        <v>-0.821926</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.954194</v>
+        <v>-0.954196</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.739812</v>
+        <v>-0.740641</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-11.771816</v>
@@ -2138,22 +2138,22 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.048835</v>
+        <v>-0.049055</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.702676</v>
+        <v>-2.74324</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.513479</v>
+        <v>-3.560215</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-16.099613</v>
+        <v>-16.114581</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.57344</v>
+        <v>-5.585328</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.721784</v>
+        <v>-2.722132</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.703061</v>
@@ -2171,16 +2171,16 @@
         <v>-1.382855</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.073638</v>
+        <v>-1.073802</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.774338</v>
+        <v>-0.774382</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.9086419999999999</v>
+        <v>-0.908644</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.696722</v>
+        <v>-0.697551</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-11.771816</v>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.002829</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.30308</v>
@@ -2477,22 +2477,22 @@
         <v>0.013993</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.130475</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.456167</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.003969</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.006833</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.002443</v>
       </c>
     </row>
     <row r="35">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.002829</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.30308</v>
@@ -2593,22 +2593,22 @@
         <v>0.013993</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.130475</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.456167</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.003969</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.006833</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.002443</v>
       </c>
     </row>
     <row r="37">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.002829</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -3289,22 +3289,22 @@
         <v>0.122692</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.28291</v>
+        <v>0.152435</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.621523</v>
+        <v>0.165356</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.167735</v>
+        <v>0.163766</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.165142</v>
+        <v>0.08354200000000001</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.071383</v>
+        <v>0.06455</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.073558</v>
+        <v>0.071115</v>
       </c>
     </row>
     <row r="49">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17296,7 +17296,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -18017,7 +18021,11 @@
           <t>Reclamation deposits 8 28,000</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -20976,7 +20984,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -29822,7 +29830,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -35084,7 +35096,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -36995,7 +37007,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -37828,7 +37840,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -45061,7 +45073,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -49301,7 +49313,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -50432,7 +50444,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">

--- a/output/pdf_financials_xlsx/BLDS.xlsx
+++ b/output/pdf_financials_xlsx/BLDS.xlsx
@@ -7038,10 +7038,10 @@
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.009667</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -28018,7 +28018,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -28323,7 +28327,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BLDS.xlsx
+++ b/output/pdf_financials_xlsx/BLDS.xlsx
@@ -1356,10 +1356,10 @@
         <v>2.746463</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.404678</v>
+        <v>0.404678</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.595653</v>
+        <v>-1.595653</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -4399,49 +4399,49 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.042675</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.08749800000000001</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.075202</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.041048</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.017281</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.01925</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.022285</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.084176</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>0</v>
@@ -4463,37 +4463,37 @@
         <v>0.213242</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.291681</v>
+        <v>0.379179</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.225303</v>
+        <v>0.300505</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.108439</v>
+        <v>0.149487</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.33554</v>
+        <v>0.35354</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.263926</v>
+        <v>0.281926</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.234232</v>
+        <v>0.251513</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.5806750000000001</v>
+        <v>0.602675</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.563644</v>
+        <v>0.582894</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>1.025872</v>
+        <v>1.044872</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.464616</v>
+        <v>0.483616</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.6812550000000001</v>
+        <v>0.700255</v>
       </c>
       <c r="P68" s="3" t="n">
         <v>0.852762</v>
@@ -4869,10 +4869,10 @@
         <v>0.533895</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.01604</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.020445</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
@@ -4896,10 +4896,10 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.042264</v>
+        <v>0.023264</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.231563</v>
+        <v>0.212563</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0.479899</v>
@@ -6983,7 +6983,7 @@
         <v>-0.054243</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011378</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016128</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.011791</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -7215,13 +7215,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.067562</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.08377800000000001</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -8355,7 +8355,7 @@
         <v>-0.054243</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011378</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -8364,13 +8364,13 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016128</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.011791</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -8413,7 +8413,7 @@
         <v>-0.974474</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.918007</v>
+        <v>-0.929385</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.202039</v>
@@ -8422,13 +8422,13 @@
         <v>-0.5729109999999999</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.083025</v>
+        <v>-1.099153</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.665772</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-1.223783</v>
+        <v>-1.235574</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-0.8577939999999999</v>
@@ -26559,7 +26559,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -27519,7 +27523,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -29537,7 +29545,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -30436,7 +30448,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -30535,7 +30551,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -30947,7 +30967,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -32058,7 +32082,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E241" s="5" t="n">
         <v>-0.015324</v>
       </c>
@@ -46782,7 +46810,11 @@
           <t>Deferred income tax recovery 17</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -47580,7 +47612,11 @@
           <t>Deferred income tax recovery (expense) 15</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -50656,7 +50692,11 @@
           <t>Future income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
